--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="2736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="2735">
   <si>
     <t>Property</t>
   </si>
@@ -8184,31 +8184,28 @@
     <t>1715</t>
   </si>
   <si>
+    <t>Prise en charge médecine nucléaire pédiatrique (0 - 5 ans)</t>
+  </si>
+  <si>
     <t>1716</t>
   </si>
   <si>
-    <t>Prise en charge médecine nucléaire pédiatrique (0 - 5 ans)</t>
+    <t>Exploration diagnostique scintigraphique splénique ou hépatosplénique</t>
   </si>
   <si>
     <t>1717</t>
   </si>
   <si>
-    <t>Exploration diagnostique scintigraphique splénique ou hépatosplénique</t>
+    <t>Exploration diagnostique scintigraphique des glandes salivaires</t>
   </si>
   <si>
     <t>1718</t>
   </si>
   <si>
-    <t>Exploration diagnostique scintigraphique des glandes salivaires</t>
+    <t>Exploration diagnostique scintigraphique aux leucocytes marqués pour recherche d'infection</t>
   </si>
   <si>
     <t>1719</t>
-  </si>
-  <si>
-    <t>Exploration diagnostique scintigraphique aux leucocytes marqués pour recherche d'infection</t>
-  </si>
-  <si>
-    <t>1720</t>
   </si>
   <si>
     <t>Recherche en oncologie, bilan d'extension</t>
@@ -8482,7 +8479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1356"/>
+  <dimension ref="A1:B1355"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -19278,44 +19275,44 @@
         <v>2722</v>
       </c>
       <c r="B1349" t="s" s="2">
-        <v>2721</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="s" s="2">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="B1350" t="s" s="2">
-        <v>2724</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="s" s="2">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="B1351" t="s" s="2">
-        <v>2726</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="s" s="2">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="B1352" t="s" s="2">
-        <v>2728</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="s" s="2">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="B1353" t="s" s="2">
-        <v>2730</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="s" s="2">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="B1354" t="s" s="2">
         <v>2732</v>
@@ -19326,15 +19323,7 @@
         <v>2733</v>
       </c>
       <c r="B1355" t="s" s="2">
-        <v>2733</v>
-      </c>
-    </row>
-    <row r="1356">
-      <c r="A1356" t="s" s="2">
         <v>2734</v>
-      </c>
-      <c r="B1356" t="s" s="2">
-        <v>2735</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -7824,7 +7824,7 @@
     <t>1655</t>
   </si>
   <si>
-    <t>Evaluation visuelle des troubles orthoptiques et neurovisuels dans le cadre des troubles du neuro-développement (TNV - TND)</t>
+    <t>Evaluation orthoptique et/ou prise en soins de la fonction visuelle et neurovisuelle dans le cadre du neurodéveloppement (TNV - TND)</t>
   </si>
   <si>
     <t>1656</t>
@@ -7836,7 +7836,7 @@
     <t>1657</t>
   </si>
   <si>
-    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
+    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
   </si>
   <si>
     <t>1658</t>
